--- a/data/external/Knee_Replacement_Missing_Values.xlsx
+++ b/data/external/Knee_Replacement_Missing_Values.xlsx
@@ -1,37 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sgbsmit-my.sharepoint.com/personal/ginoh_sgb-smit_group/Documents/Documents/GitHub/EAISI-NHS/data/external/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_23F921ED1F330B3DA32C4C33DD4DF66D66EABB76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{730B4577-5AC5-4B95-8285-C49AAAC90A87}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -218,8 +196,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,298 +260,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>ColumnName</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Knee Replacement Pre-Op Q Confidence</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>Knee Replacement Pre-Op Q Kneeling</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>Knee Replacement Pre-Op Q Limping</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Knee Replacement Pre-Op Q Night Pain</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Knee Replacement Pre-Op Q Pain</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Knee Replacement Pre-Op Q Score</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>Arthritis</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>Cancer</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>Circulation</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>Depression</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>Diabetes</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>Heart Disease</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>High Bp</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>Kidney Disease</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>Liver Disease</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>Lung Disease</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>Nervous System</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>Stroke</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>Age Band</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>Gender</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>Knee Replacement OKS Post-Op Q Predicted</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>Knee Replacement Pre-Op Q Shopping</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>Knee Replacement Pre-Op Q Stairs</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>Knee Replacement Pre-Op Q Standing</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>Knee Replacement Pre-Op Q Transport</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>Knee Replacement Pre-Op Q Walking</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>Knee Replacement Pre-Op Q Washing</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>Knee Replacement Pre-Op Q Work</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>Post-Op Q EQ VAS</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>Post-Op Q EQ5D Index Profile</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>Pre-Op Q Activity</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>Pre-Op Q Anxiety</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>Pre-Op Q Assisted</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>Pre-Op Q Assisted By</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>Pre-Op Q Disability</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>Pre-Op Q Discomfort</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>Pre-Op Q EQ VAS</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>Pre-Op Q EQ5D Index</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>Pre-Op Q EQ5D Index Profile</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41" t="str">
-            <v>Pre-Op Q Living Arrangements</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42" t="str">
-            <v>Pre-Op Q Mobility</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>Pre-Op Q Previous Surgery</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44" t="str">
-            <v>Pre-Op Q Self-Care</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45" t="str">
-            <v>Pre-Op Q Symptom Period</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46" t="str">
-            <v>Procedure</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47" t="str">
-            <v>Provider Code</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>Revision Flag</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49" t="str">
-            <v>Year</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50" t="str">
-            <v>Knee Replacement Post-Op Q Score</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51" t="str">
-            <v>Knee Replacement EQ 5D Index Post-Op Q Predicted</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52" t="str">
-            <v>Knee Replacement EQ VAS_Post-Op Q Predicted</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -611,7 +304,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -645,7 +338,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -680,10 +372,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -856,11 +547,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -877,7 +568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -893,12 +584,8 @@
       <c r="E2">
         <v>100</v>
       </c>
-      <c r="F2" t="str">
-        <f>VLOOKUP(A2,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Provider Code</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -914,12 +601,8 @@
       <c r="E3">
         <v>100</v>
       </c>
-      <c r="F3" t="str">
-        <f>VLOOKUP(A3,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Procedure</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -935,12 +618,8 @@
       <c r="E4">
         <v>100</v>
       </c>
-      <c r="F4" t="str">
-        <f>VLOOKUP(A4,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Revision Flag</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -956,12 +635,8 @@
       <c r="E5">
         <v>100</v>
       </c>
-      <c r="F5" t="str">
-        <f>VLOOKUP(A5,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Year</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -977,12 +652,8 @@
       <c r="E6">
         <v>100</v>
       </c>
-      <c r="F6" t="str">
-        <f>VLOOKUP(A6,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Assisted By</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -998,12 +669,8 @@
       <c r="E7">
         <v>100</v>
       </c>
-      <c r="F7" t="str">
-        <f>VLOOKUP(A7,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Lung Disease</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1019,12 +686,8 @@
       <c r="E8">
         <v>100</v>
       </c>
-      <c r="F8" t="str">
-        <f>VLOOKUP(A8,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Diabetes</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1040,12 +703,8 @@
       <c r="E9">
         <v>100</v>
       </c>
-      <c r="F9" t="str">
-        <f>VLOOKUP(A9,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Circulation</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1061,12 +720,8 @@
       <c r="E10">
         <v>100</v>
       </c>
-      <c r="F10" t="str">
-        <f>VLOOKUP(A10,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Stroke</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1082,12 +737,8 @@
       <c r="E11">
         <v>100</v>
       </c>
-      <c r="F11" t="str">
-        <f>VLOOKUP(A11,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>High Bp</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1103,12 +754,8 @@
       <c r="E12">
         <v>100</v>
       </c>
-      <c r="F12" t="str">
-        <f>VLOOKUP(A12,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Heart Disease</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1124,12 +771,8 @@
       <c r="E13">
         <v>100</v>
       </c>
-      <c r="F13" t="str">
-        <f>VLOOKUP(A13,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Kidney Disease</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1145,12 +788,8 @@
       <c r="E14">
         <v>100</v>
       </c>
-      <c r="F14" t="str">
-        <f>VLOOKUP(A14,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Post-Op Q EQ5D Index Profile</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1166,12 +805,8 @@
       <c r="E15">
         <v>100</v>
       </c>
-      <c r="F15" t="str">
-        <f>VLOOKUP(A15,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q EQ5D Index Profile</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1187,12 +822,8 @@
       <c r="E16">
         <v>100</v>
       </c>
-      <c r="F16" t="str">
-        <f>VLOOKUP(A16,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Arthritis</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1208,12 +839,8 @@
       <c r="E17">
         <v>100</v>
       </c>
-      <c r="F17" t="str">
-        <f>VLOOKUP(A17,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Depression</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1229,12 +856,8 @@
       <c r="E18">
         <v>100</v>
       </c>
-      <c r="F18" t="str">
-        <f>VLOOKUP(A18,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Cancer</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1250,12 +873,8 @@
       <c r="E19">
         <v>100</v>
       </c>
-      <c r="F19" t="str">
-        <f>VLOOKUP(A19,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Liver Disease</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1271,12 +890,8 @@
       <c r="E20">
         <v>100</v>
       </c>
-      <c r="F20" t="str">
-        <f>VLOOKUP(A20,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Nervous System</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1292,12 +907,8 @@
       <c r="E21">
         <v>99.98</v>
       </c>
-      <c r="F21" t="str">
-        <f>VLOOKUP(A21,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Post-Op Q EQ VAS</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1313,12 +924,8 @@
       <c r="E22">
         <v>99.98</v>
       </c>
-      <c r="F22" t="str">
-        <f>VLOOKUP(A22,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q EQ VAS</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1334,12 +941,8 @@
       <c r="E23">
         <v>99.91</v>
       </c>
-      <c r="F23" t="str">
-        <f>VLOOKUP(A23,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Washing</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1355,12 +958,8 @@
       <c r="E24">
         <v>99.86</v>
       </c>
-      <c r="F24" t="str">
-        <f>VLOOKUP(A24,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Pain</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1376,12 +975,8 @@
       <c r="E25">
         <v>99.25</v>
       </c>
-      <c r="F25" t="str">
-        <f>VLOOKUP(A25,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Previous Surgery</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1397,12 +992,8 @@
       <c r="E26">
         <v>99.12</v>
       </c>
-      <c r="F26" t="str">
-        <f>VLOOKUP(A26,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Symptom Period</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1418,12 +1009,8 @@
       <c r="E27">
         <v>99.05</v>
       </c>
-      <c r="F27" t="str">
-        <f>VLOOKUP(A27,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Night Pain</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1439,12 +1026,8 @@
       <c r="E28">
         <v>99.03</v>
       </c>
-      <c r="F28" t="str">
-        <f>VLOOKUP(A28,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Shopping</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1460,12 +1043,8 @@
       <c r="E29">
         <v>99.03</v>
       </c>
-      <c r="F29" t="str">
-        <f>VLOOKUP(A29,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Stairs</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1481,12 +1060,8 @@
       <c r="E30">
         <v>99.03</v>
       </c>
-      <c r="F30" t="str">
-        <f>VLOOKUP(A30,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Confidence</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1502,12 +1077,8 @@
       <c r="E31">
         <v>99.02</v>
       </c>
-      <c r="F31" t="str">
-        <f>VLOOKUP(A31,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Transport</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1523,12 +1094,8 @@
       <c r="E32">
         <v>99.02</v>
       </c>
-      <c r="F32" t="str">
-        <f>VLOOKUP(A32,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Work</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1542,14 +1109,10 @@
         <v>1396</v>
       </c>
       <c r="E33">
-        <v>98.99</v>
-      </c>
-      <c r="F33" t="str">
-        <f>VLOOKUP(A33,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Kneeling</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>98.98999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1565,12 +1128,8 @@
       <c r="E34">
         <v>98.97</v>
       </c>
-      <c r="F34" t="str">
-        <f>VLOOKUP(A34,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Limping</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1586,12 +1145,8 @@
       <c r="E35">
         <v>98.95</v>
       </c>
-      <c r="F35" t="str">
-        <f>VLOOKUP(A35,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Standing</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1607,12 +1162,8 @@
       <c r="E36">
         <v>98.95</v>
       </c>
-      <c r="F36" t="str">
-        <f>VLOOKUP(A36,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Walking</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1626,14 +1177,10 @@
         <v>1511</v>
       </c>
       <c r="E37">
-        <v>98.9</v>
-      </c>
-      <c r="F37" t="str">
-        <f>VLOOKUP(A37,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Assisted</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1649,12 +1196,8 @@
       <c r="E38">
         <v>98.48</v>
       </c>
-      <c r="F38" t="str">
-        <f>VLOOKUP(A38,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Living Arrangements</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1670,12 +1213,8 @@
       <c r="E39">
         <v>97.83</v>
       </c>
-      <c r="F39" t="str">
-        <f>VLOOKUP(A39,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Post-Op Q Score</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1689,14 +1228,10 @@
         <v>4286</v>
       </c>
       <c r="E40">
-        <v>96.82</v>
-      </c>
-      <c r="F40" t="str">
-        <f>VLOOKUP(A40,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Mobility</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>96.81999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1712,12 +1247,8 @@
       <c r="E41">
         <v>96.73</v>
       </c>
-      <c r="F41" t="str">
-        <f>VLOOKUP(A41,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Self-Care</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1733,12 +1264,8 @@
       <c r="E42">
         <v>96.67</v>
       </c>
-      <c r="F42" t="str">
-        <f>VLOOKUP(A42,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Activity</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1752,14 +1279,10 @@
         <v>5161</v>
       </c>
       <c r="E43">
-        <v>96.15</v>
-      </c>
-      <c r="F43" t="str">
-        <f>VLOOKUP(A43,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Anxiety</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <v>96.15000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -1775,12 +1298,8 @@
       <c r="E44">
         <v>95.98</v>
       </c>
-      <c r="F44" t="str">
-        <f>VLOOKUP(A44,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement OKS Post-Op Q Predicted</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1796,12 +1315,8 @@
       <c r="E45">
         <v>95.87</v>
       </c>
-      <c r="F45" t="str">
-        <f>VLOOKUP(A45,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement Pre-Op Q Score</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1817,12 +1332,8 @@
       <c r="E46">
         <v>95.86</v>
       </c>
-      <c r="F46" t="str">
-        <f>VLOOKUP(A46,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Discomfort</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -1836,14 +1347,10 @@
         <v>5907</v>
       </c>
       <c r="E47">
-        <v>95.57</v>
-      </c>
-      <c r="F47" t="str">
-        <f>VLOOKUP(A47,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q Disability</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+        <v>95.56999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -1859,12 +1366,8 @@
       <c r="E48">
         <v>94.31</v>
       </c>
-      <c r="F48" t="str">
-        <f>VLOOKUP(A48,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Pre-Op Q EQ5D Index</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1878,14 +1381,10 @@
         <v>9402</v>
       </c>
       <c r="E49">
-        <v>92.76</v>
-      </c>
-      <c r="F49" t="str">
-        <f>VLOOKUP(A49,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Gender</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92.76000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -1899,14 +1398,10 @@
         <v>9402</v>
       </c>
       <c r="E50">
-        <v>92.76</v>
-      </c>
-      <c r="F50" t="str">
-        <f>VLOOKUP(A50,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Age Band</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92.76000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -1922,12 +1417,8 @@
       <c r="E51">
         <v>88.53</v>
       </c>
-      <c r="F51" t="str">
-        <f>VLOOKUP(A51,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement EQ 5D Index Post-Op Q Predicted</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1941,11 +1432,7 @@
         <v>19423</v>
       </c>
       <c r="E52">
-        <v>83.79</v>
-      </c>
-      <c r="F52" t="str">
-        <f>VLOOKUP(A52,[1]Sheet1!$A:$A,1,FALSE)</f>
-        <v>Knee Replacement EQ VAS_Post-Op Q Predicted</v>
+        <v>83.79000000000001</v>
       </c>
     </row>
   </sheetData>
